--- a/speech_tokens.xlsx
+++ b/speech_tokens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davel\data\Code\WearOS\TalkRPN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93321F9-90B5-4A3B-A95F-FED93135AC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730F9443-19EF-4229-BFB9-E29F30597979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67632" yWindow="3240" windowWidth="21480" windowHeight="17268" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="58128" yWindow="2172" windowWidth="21480" windowHeight="17268" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="175">
   <si>
     <t>Say</t>
   </si>
@@ -60,9 +60,6 @@
     <t>tan^-1</t>
   </si>
   <si>
-    <t>x&lt;&gt;y swap</t>
-  </si>
-  <si>
     <t>Convert to rectangular</t>
   </si>
   <si>
@@ -264,9 +261,6 @@
     <t>last x</t>
   </si>
   <si>
-    <t>squirt</t>
-  </si>
-  <si>
     <t>l n</t>
   </si>
   <si>
@@ -321,12 +315,6 @@
     <t>imperial</t>
   </si>
   <si>
-    <t xml:space="preserve">S A E </t>
-  </si>
-  <si>
-    <t>english</t>
-  </si>
-  <si>
     <t>Set SI units mode</t>
   </si>
   <si>
@@ -354,18 +342,6 @@
     <t>back</t>
   </si>
   <si>
-    <t>DROP</t>
-  </si>
-  <si>
-    <t>ROT</t>
-  </si>
-  <si>
-    <t>rot</t>
-  </si>
-  <si>
-    <t>rotate</t>
-  </si>
-  <si>
     <t>drop</t>
   </si>
   <si>
@@ -375,9 +351,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>When switching units, all values in all storage that have unit attributes get converted to the newly selected system (gallons become liters, etc.)</t>
-  </si>
-  <si>
     <t>redo</t>
   </si>
   <si>
@@ -387,12 +360,6 @@
     <t>Redo undoes undo.</t>
   </si>
   <si>
-    <t>Forth</t>
-  </si>
-  <si>
-    <t>EEX</t>
-  </si>
-  <si>
     <t>ENG</t>
   </si>
   <si>
@@ -534,9 +501,6 @@
     <t>"e" is acceptable as n to get the natural log</t>
   </si>
   <si>
-    <t>Special case - 'e' after 1 or more digits entered into X is EEX; otherwise it's the constant 2.71828...</t>
-  </si>
-  <si>
     <t>antilog base n</t>
   </si>
   <si>
@@ -550,6 +514,42 @@
   </si>
   <si>
     <t>Swaps commas and dots</t>
+  </si>
+  <si>
+    <t>M K S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U S </t>
+  </si>
+  <si>
+    <t>Set US customary units mode</t>
+  </si>
+  <si>
+    <t>Automatically switch units mode if user inputs a unit in a mode (if in SI mode and user inputs feet, switch to US, converting all values)</t>
+  </si>
+  <si>
+    <t>Switch only if a unit is entered that's incompatible with current setting. "Seconds" never changes unit mode. "Gallons" sets US unless</t>
+  </si>
+  <si>
+    <t>already in Imperial mode (gallons is compatible with Imperial, too). The word "Imperial" in a unit sets Imperial mode, "US" sets US mode.</t>
+  </si>
+  <si>
+    <t>british</t>
+  </si>
+  <si>
+    <t>american</t>
+  </si>
+  <si>
+    <t>Named variables:</t>
+  </si>
+  <si>
+    <t>Special case - 'e' after &gt; 0 digits entered into X is EEX; otherwise it's the base of the natural logs.</t>
+  </si>
+  <si>
+    <t>EEX or e</t>
+  </si>
+  <si>
+    <t>c l r</t>
   </si>
 </sst>
 </file>
@@ -593,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -605,12 +605,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -893,14 +887,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" style="2" customWidth="1"/>
+    <col min="1" max="1" width="22.88671875" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.21875" style="2" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="2"/>
-    <col min="5" max="5" width="25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.5546875" style="2" customWidth="1"/>
     <col min="6" max="8" width="8.88671875" style="4"/>
     <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
@@ -919,22 +913,22 @@
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -944,23 +938,23 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="4" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2">
         <v>2</v>
@@ -968,7 +962,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2">
         <v>3</v>
@@ -976,7 +970,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2">
         <v>4</v>
@@ -984,10 +978,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="E7" s="2">
         <v>5</v>
@@ -995,7 +989,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
@@ -1003,7 +997,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2">
         <v>7</v>
@@ -1011,7 +1005,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2">
         <v>8</v>
@@ -1019,10 +1013,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="E11" s="2">
         <v>9</v>
@@ -1030,10 +1024,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>2</v>
@@ -1041,13 +1035,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1055,10 +1049,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>4</v>
@@ -1066,7 +1060,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>5</v>
@@ -1074,172 +1068,170 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E22" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="2" t="s">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>16</v>
@@ -1247,10 +1239,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>17</v>
@@ -1258,10 +1250,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>18</v>
@@ -1271,16 +1263,19 @@
       <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="B36" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="E36" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>20</v>
@@ -1288,69 +1283,66 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>47</v>
+        <v>66</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B40" s="2" t="s">
         <v>68</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1363,333 +1355,323 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>75</v>
+        <v>111</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>88</v>
       </c>
+      <c r="B60" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="E60" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="E62" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F66" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="E70" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F68" s="4" t="s">
+      <c r="B71" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
-        <v>151</v>
+      <c r="A77" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>147</v>
+      <c r="A86" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="B89" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="F90" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
